--- a/data/LCIs/Lai_2025/Cu_LCIs_BW_Final_v2.xlsx
+++ b/data/LCIs/Lai_2025/Cu_LCIs_BW_Final_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/data/LCIs/Lai_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{33880131-7A62-4ED1-9ECB-5FC19B6F587E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDD7E7B4-B365-4A74-9551-7865B4A0AD3D}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{33880131-7A62-4ED1-9ECB-5FC19B6F587E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{729934D8-03F1-4502-BD71-395FB7BFE3CD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,8 @@
     <sheet name="PR11_Cu_AU" sheetId="12" r:id="rId13"/>
     <sheet name="PR12_Cu_US_Pyro" sheetId="13" r:id="rId14"/>
     <sheet name="PR13_Cu_SE_Pyro" sheetId="28" r:id="rId15"/>
-    <sheet name="PR14_Cu_PO_ShaftFurnace" sheetId="34" r:id="rId16"/>
-    <sheet name="PR15_Cu_PO_FlashFurnace" sheetId="35" r:id="rId17"/>
+    <sheet name="PR14_Cu_PL_ShaftFurnace" sheetId="34" r:id="rId16"/>
+    <sheet name="PR15_Cu_PL_FlashFurnace" sheetId="35" r:id="rId17"/>
     <sheet name="PR16_Cu_CN_Pyro" sheetId="37" r:id="rId18"/>
     <sheet name="PR17_Cu_CD_Hydro" sheetId="38" r:id="rId19"/>
   </sheets>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5320" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5320" uniqueCount="418">
   <si>
     <t>Activity</t>
   </si>
@@ -341,9 +341,6 @@
     <t>High-grade WEEE</t>
   </si>
   <si>
-    <t>Europe</t>
-  </si>
-  <si>
     <t xml:space="preserve">[C] WEEE pre-treatment </t>
   </si>
   <si>
@@ -1023,9 +1020,6 @@
   </si>
   <si>
     <t>[P+R] Copper (Cu) cathode production - Shaft Furnace (Pyrometallurgy)</t>
-  </si>
-  <si>
-    <t>PO</t>
   </si>
   <si>
     <t>copper mine operation and beneficiation, sulfide ore</t>
@@ -1742,9 +1736,6 @@
     </r>
   </si>
   <si>
-    <t>PR14_Cu_PO_ShaftFurnace</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1830,9 +1821,6 @@
       </rPr>
       <t>Applied AF: "copper concentrate, sulfide ore" input = 99.8%.</t>
     </r>
-  </si>
-  <si>
-    <t>PR15_Cu_PO_FlashFurnace</t>
   </si>
   <si>
     <t>PR16_Cu_CN_Pyro</t>
@@ -3062,6 +3050,15 @@
   <si>
     <t>Water, salt, ocean</t>
   </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>PR14_Cu_PL_ShaftFurnace</t>
+  </si>
+  <si>
+    <t>PR15_Cu_PL_FlashFurnace</t>
+  </si>
 </sst>
 </file>
 
@@ -3734,12 +3731,12 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="38" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C2" s="39"/>
       <c r="D2" s="39"/>
@@ -4282,10 +4279,10 @@
     <row r="32" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="29" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="25"/>
@@ -4298,10 +4295,10 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D34" s="32"/>
       <c r="E34" s="32"/>
@@ -4314,7 +4311,7 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="30" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>56</v>
@@ -4330,7 +4327,7 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="30" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>61</v>
@@ -4346,7 +4343,7 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="30" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>94</v>
@@ -4362,10 +4359,10 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="30" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D38" s="32"/>
       <c r="E38" s="32"/>
@@ -4378,10 +4375,10 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="30" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D39" s="32"/>
       <c r="E39" s="32"/>
@@ -4394,10 +4391,10 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="30" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D40" s="32"/>
       <c r="E40" s="32"/>
@@ -4410,10 +4407,10 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="30" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D41" s="32"/>
       <c r="E41" s="32"/>
@@ -4426,10 +4423,10 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="30" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D42" s="32"/>
       <c r="E42" s="32"/>
@@ -4442,10 +4439,10 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="30" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D43" s="32"/>
       <c r="E43" s="32"/>
@@ -4458,10 +4455,10 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="30" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D44" s="32"/>
       <c r="E44" s="32"/>
@@ -4474,10 +4471,10 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="30" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D45" s="32"/>
       <c r="E45" s="32"/>
@@ -4490,10 +4487,10 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="30" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D46" s="32"/>
       <c r="E46" s="32"/>
@@ -4506,10 +4503,10 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="30" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D47" s="32"/>
       <c r="E47" s="32"/>
@@ -4522,10 +4519,10 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="30" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D48" s="32"/>
       <c r="E48" s="32"/>
@@ -4538,10 +4535,10 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="30" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D49" s="32"/>
       <c r="E49" s="32"/>
@@ -4554,10 +4551,10 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="30" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D50" s="32"/>
       <c r="E50" s="32"/>
@@ -4570,10 +4567,10 @@
     </row>
     <row r="51" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="31" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D51" s="26"/>
       <c r="E51" s="26"/>
@@ -4641,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -4657,7 +4654,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -4735,13 +4732,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -4758,10 +4755,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
@@ -4779,7 +4776,7 @@
         <v>26</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -4805,7 +4802,7 @@
         <v>26</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -4831,15 +4828,15 @@
         <v>26</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>30</v>
@@ -4857,15 +4854,15 @@
         <v>26</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>30</v>
@@ -4883,7 +4880,7 @@
         <v>26</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -4909,7 +4906,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -4920,7 +4917,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D16" s="1">
         <v>0.65</v>
@@ -4935,15 +4932,15 @@
         <v>26</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -4961,15 +4958,15 @@
         <v>26</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>30</v>
@@ -4987,15 +4984,15 @@
         <v>26</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>
@@ -5013,15 +5010,15 @@
         <v>26</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>30</v>
@@ -5039,7 +5036,7 @@
         <v>26</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -5062,7 +5059,7 @@
         <v>46</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -5085,12 +5082,12 @@
         <v>46</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" s="1">
         <v>3.8075999999999999</v>
@@ -5108,12 +5105,12 @@
         <v>86</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D24" s="1">
         <v>1.7081999999999999</v>
@@ -5131,7 +5128,7 @@
         <v>86</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -5154,12 +5151,12 @@
         <v>86</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D26" s="1">
         <v>4.29</v>
@@ -5177,12 +5174,12 @@
         <v>86</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D27" s="1">
         <v>7.76E-4</v>
@@ -5200,12 +5197,12 @@
         <v>86</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D28" s="1">
         <v>2.9000000000000001E-2</v>
@@ -5220,15 +5217,15 @@
         <v>45</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" s="1">
         <v>1.25E-3</v>
@@ -5246,7 +5243,7 @@
         <v>86</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -5269,7 +5266,7 @@
         <v>86</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -5292,7 +5289,7 @@
         <v>86</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -5301,7 +5298,7 @@
         <v>0</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -5317,7 +5314,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -5395,13 +5392,13 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -5418,13 +5415,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D42" s="1">
         <v>1</v>
@@ -5473,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -5489,7 +5486,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -5513,7 +5510,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -5567,13 +5564,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -5611,7 +5608,7 @@
         <v>26</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -5622,7 +5619,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D11" s="12">
         <v>0.36929078014184402</v>
@@ -5637,7 +5634,7 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -5663,15 +5660,15 @@
         <v>26</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>30</v>
@@ -5689,15 +5686,15 @@
         <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>201</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>202</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>30</v>
@@ -5715,15 +5712,15 @@
         <v>26</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>30</v>
@@ -5741,7 +5738,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -5752,7 +5749,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D16" s="12">
         <v>0.16072722801339109</v>
@@ -5767,7 +5764,7 @@
         <v>26</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -5793,15 +5790,15 @@
         <v>26</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>30</v>
@@ -5819,7 +5816,7 @@
         <v>26</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -5830,7 +5827,7 @@
         <v>38</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D19" s="12">
         <v>0.1139890840433465</v>
@@ -5845,15 +5842,15 @@
         <v>26</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>201</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>202</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>30</v>
@@ -5871,15 +5868,15 @@
         <v>26</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>203</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>204</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>30</v>
@@ -5897,7 +5894,7 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -5908,7 +5905,7 @@
         <v>38</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D22" s="12">
         <v>0.01</v>
@@ -5923,15 +5920,15 @@
         <v>26</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>30</v>
@@ -5949,15 +5946,15 @@
         <v>26</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>201</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>202</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>30</v>
@@ -5975,7 +5972,7 @@
         <v>26</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -5986,7 +5983,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D25" s="12">
         <v>0.37</v>
@@ -6001,7 +5998,7 @@
         <v>26</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -6010,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -6026,7 +6023,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -6104,13 +6101,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
@@ -6127,13 +6124,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
@@ -6182,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -6190,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -6198,7 +6195,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -6222,7 +6219,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -6276,13 +6273,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>207</v>
-      </c>
       <c r="C9" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -6305,7 +6302,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D10" s="12">
         <v>3.8429999999999999E-2</v>
@@ -6320,7 +6317,7 @@
         <v>26</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -6331,7 +6328,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D11" s="12">
         <v>0.14399999999999999</v>
@@ -6346,7 +6343,7 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -6372,7 +6369,7 @@
         <v>26</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -6398,7 +6395,7 @@
         <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -6424,7 +6421,7 @@
         <v>26</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -6447,7 +6444,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -6470,12 +6467,12 @@
         <v>86</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D17" s="12">
         <v>3.4000000000000002E-2</v>
@@ -6493,7 +6490,7 @@
         <v>86</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -6516,12 +6513,12 @@
         <v>86</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D19" s="12">
         <v>6.0000000000000002E-5</v>
@@ -6539,12 +6536,12 @@
         <v>86</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D20" s="12">
         <v>0.16700000000000001</v>
@@ -6562,7 +6559,7 @@
         <v>86</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -6585,12 +6582,12 @@
         <v>86</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" s="12">
         <v>6.0000000000000002E-5</v>
@@ -6608,7 +6605,7 @@
         <v>86</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -6631,7 +6628,7 @@
         <v>86</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -6640,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -6656,7 +6653,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -6734,13 +6731,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -6763,7 +6760,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D34" s="12">
         <v>1.25</v>
@@ -6778,7 +6775,7 @@
         <v>26</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -6789,7 +6786,7 @@
         <v>38</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D35" s="12">
         <v>1.0000000000000001E-5</v>
@@ -6804,7 +6801,7 @@
         <v>26</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -6815,7 +6812,7 @@
         <v>38</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D36" s="12">
         <v>2</v>
@@ -6830,7 +6827,7 @@
         <v>26</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -6856,7 +6853,7 @@
         <v>26</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -6882,7 +6879,7 @@
         <v>26</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -6908,7 +6905,7 @@
         <v>26</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -6934,7 +6931,7 @@
         <v>26</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -6960,7 +6957,7 @@
         <v>26</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -6983,7 +6980,7 @@
         <v>46</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -6992,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -7008,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -7086,13 +7083,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D52" s="12">
         <v>1</v>
@@ -7109,13 +7106,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D53" s="12">
         <v>1</v>
@@ -7132,13 +7129,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B54" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>207</v>
-      </c>
       <c r="C54" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D54" s="12">
         <v>1</v>
@@ -7188,7 +7185,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -7196,7 +7193,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -7204,7 +7201,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -7282,13 +7279,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>212</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>213</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -7326,7 +7323,7 @@
         <v>26</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -7352,7 +7349,7 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -7378,7 +7375,7 @@
         <v>26</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -7404,7 +7401,7 @@
         <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -7415,7 +7412,7 @@
         <v>38</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D14" s="12">
         <v>8.0000000000000002E-3</v>
@@ -7430,7 +7427,7 @@
         <v>26</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -7441,7 +7438,7 @@
         <v>38</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D15" s="12">
         <v>3.8E-3</v>
@@ -7456,7 +7453,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -7467,7 +7464,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D16" s="12">
         <v>1.8499999999999999E-2</v>
@@ -7482,7 +7479,7 @@
         <v>26</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -7493,7 +7490,7 @@
         <v>38</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D17" s="12">
         <v>7.4999999999999997E-3</v>
@@ -7508,15 +7505,15 @@
         <v>26</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>30</v>
@@ -7534,15 +7531,15 @@
         <v>26</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>215</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>216</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>24</v>
@@ -7560,15 +7557,15 @@
         <v>26</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>217</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>218</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>30</v>
@@ -7586,7 +7583,7 @@
         <v>26</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -7612,15 +7609,15 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>185</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>186</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>30</v>
@@ -7638,7 +7635,7 @@
         <v>26</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -7667,7 +7664,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -7683,7 +7680,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -7707,7 +7704,7 @@
         <v>8</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -7761,13 +7758,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -7784,13 +7781,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>212</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>213</v>
       </c>
       <c r="D34" s="12">
         <v>3.65</v>
@@ -7807,10 +7804,10 @@
     </row>
     <row r="35" spans="1:7" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>24</v>
@@ -7830,10 +7827,10 @@
     </row>
     <row r="36" spans="1:7" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>30</v>
@@ -7886,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -7894,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -7902,7 +7899,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -7926,7 +7923,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -7980,13 +7977,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>220</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>221</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -8009,7 +8006,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D10" s="12">
         <v>0.25</v>
@@ -8024,15 +8021,15 @@
         <v>26</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>222</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>223</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>24</v>
@@ -8050,7 +8047,7 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -8073,7 +8070,7 @@
         <v>86</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -8082,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -8098,7 +8095,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -8122,7 +8119,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -8176,13 +8173,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D22" s="12">
         <v>1</v>
@@ -8205,7 +8202,7 @@
         <v>38</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D23" s="12">
         <v>1.444444444444444</v>
@@ -8220,15 +8217,15 @@
         <v>26</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>227</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>228</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>30</v>
@@ -8246,15 +8243,15 @@
         <v>26</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>30</v>
@@ -8272,15 +8269,15 @@
         <v>26</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>222</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>223</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>24</v>
@@ -8298,12 +8295,12 @@
         <v>26</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D27" s="12">
         <v>1.5E-3</v>
@@ -8321,12 +8318,12 @@
         <v>86</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D28" s="12">
         <v>4.9999999999999998E-7</v>
@@ -8344,7 +8341,7 @@
         <v>86</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -8367,7 +8364,7 @@
         <v>86</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -8390,12 +8387,12 @@
         <v>86</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D31" s="12">
         <v>4.9999999999999998E-7</v>
@@ -8413,7 +8410,7 @@
         <v>86</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -8436,12 +8433,12 @@
         <v>86</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" s="12">
         <v>1E-8</v>
@@ -8459,7 +8456,7 @@
         <v>86</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -8482,12 +8479,12 @@
         <v>86</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D35" s="12">
         <v>5.0999999999999999E-7</v>
@@ -8505,7 +8502,7 @@
         <v>86</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -8528,12 +8525,12 @@
         <v>86</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D37" s="12">
         <v>4.9999999999999998E-7</v>
@@ -8551,12 +8548,12 @@
         <v>86</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D38" s="12">
         <v>4.9999999999999998E-7</v>
@@ -8574,12 +8571,12 @@
         <v>86</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D39" s="12">
         <v>2.9999999999999999E-7</v>
@@ -8597,12 +8594,12 @@
         <v>86</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D40" s="12">
         <v>9.9999999999999995E-7</v>
@@ -8620,12 +8617,12 @@
         <v>86</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D41" s="12">
         <v>2.9999999999999999E-7</v>
@@ -8643,7 +8640,7 @@
         <v>83</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -8666,7 +8663,7 @@
         <v>83</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -8689,12 +8686,12 @@
         <v>83</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D44" s="12">
         <v>2.600000000000001E-7</v>
@@ -8712,7 +8709,7 @@
         <v>83</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -8735,12 +8732,12 @@
         <v>83</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46" s="12">
         <v>3.9999999999999986E-9</v>
@@ -8758,7 +8755,7 @@
         <v>83</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -8781,12 +8778,12 @@
         <v>83</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D48" s="12">
         <v>7.7000000000000004E-7</v>
@@ -8804,7 +8801,7 @@
         <v>83</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -8827,12 +8824,12 @@
         <v>83</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D50" s="12">
         <v>2.9999999999999999E-7</v>
@@ -8850,12 +8847,12 @@
         <v>83</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D51" s="12">
         <v>1.1999999999999999E-6</v>
@@ -8873,12 +8870,12 @@
         <v>83</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D52" s="12">
         <v>2.9999999999999999E-7</v>
@@ -8896,12 +8893,12 @@
         <v>83</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D53" s="12">
         <v>7.7000000000000004E-7</v>
@@ -8919,7 +8916,7 @@
         <v>83</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -8928,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -8944,7 +8941,7 @@
         <v>3</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -9022,13 +9019,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D63" s="12">
         <v>1</v>
@@ -9045,13 +9042,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D64" s="12">
         <v>1</v>
@@ -9068,13 +9065,13 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>220</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>221</v>
       </c>
       <c r="D65" s="12">
         <v>1</v>
@@ -9123,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -9131,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -9139,7 +9136,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -9217,13 +9214,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -9261,18 +9258,18 @@
         <v>26</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" s="12">
         <v>0.2417770559805896</v>
@@ -9287,15 +9284,15 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>236</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>237</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>30</v>
@@ -9313,7 +9310,7 @@
         <v>26</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -9339,18 +9336,18 @@
         <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>154</v>
-      </c>
       <c r="C14" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D14" s="12">
         <v>2.582490330743992E-2</v>
@@ -9365,15 +9362,15 @@
         <v>26</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>238</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>239</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>24</v>
@@ -9391,15 +9388,15 @@
         <v>26</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>240</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>241</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>24</v>
@@ -9417,18 +9414,18 @@
         <v>26</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D17" s="12">
         <v>2.2461111002406691</v>
@@ -9443,15 +9440,15 @@
         <v>26</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>236</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>237</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>30</v>
@@ -9469,15 +9466,15 @@
         <v>26</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>242</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>243</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>24</v>
@@ -9495,7 +9492,7 @@
         <v>26</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -9521,18 +9518,18 @@
         <v>26</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>129</v>
-      </c>
       <c r="C21" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D21" s="12">
         <v>2.5436828614475492E-6</v>
@@ -9547,24 +9544,24 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>245</v>
-      </c>
       <c r="C22" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D22" s="12">
         <v>0.40999999999999959</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>25</v>
@@ -9573,15 +9570,15 @@
         <v>26</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>247</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>24</v>
@@ -9599,15 +9596,15 @@
         <v>26</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>249</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>30</v>
@@ -9625,18 +9622,18 @@
         <v>26</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>251</v>
-      </c>
       <c r="C25" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D25" s="12">
         <v>-1.754488948024079E-3</v>
@@ -9651,15 +9648,15 @@
         <v>26</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>253</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>30</v>
@@ -9677,18 +9674,18 @@
         <v>26</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="C27" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D27" s="12">
         <v>-1.4022867056698031E-4</v>
@@ -9703,18 +9700,18 @@
         <v>26</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="C28" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D28" s="12">
         <v>-1.0370399358209239E-4</v>
@@ -9729,18 +9726,18 @@
         <v>26</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="C29" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D29" s="12">
         <v>-1.177268606387904E-4</v>
@@ -9755,18 +9752,18 @@
         <v>26</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="C30" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D30" s="12">
         <v>-7.1744901220315452E-5</v>
@@ -9781,18 +9778,18 @@
         <v>26</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="C31" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D31" s="12">
         <v>-3.913358248380844E-5</v>
@@ -9807,18 +9804,18 @@
         <v>26</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="C32" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D32" s="12">
         <v>-1.819711585497093E-5</v>
@@ -9833,18 +9830,18 @@
         <v>26</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D33" s="12">
         <v>8.1528296841267583E-2</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>44</v>
@@ -9853,10 +9850,10 @@
         <v>45</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -9879,12 +9876,12 @@
         <v>46</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D35" s="12">
         <v>1.9566791241904229E-3</v>
@@ -9899,15 +9896,15 @@
         <v>45</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D36" s="12">
         <v>3.2611318736507132E-4</v>
@@ -9922,10 +9919,10 @@
         <v>45</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -9948,12 +9945,12 @@
         <v>86</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D38" s="12">
         <v>1.2392301119872669E-3</v>
@@ -9971,7 +9968,7 @@
         <v>86</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -9994,12 +9991,12 @@
         <v>83</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" s="12">
         <v>7.5593036831223307E-6</v>
@@ -10017,7 +10014,7 @@
         <v>83</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -10040,7 +10037,7 @@
         <v>83</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -10063,7 +10060,7 @@
         <v>83</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -10086,7 +10083,7 @@
         <v>83</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -10109,12 +10106,12 @@
         <v>83</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D45" s="12">
         <v>8.5767768277013486E-9</v>
@@ -10132,12 +10129,12 @@
         <v>83</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46" s="12">
         <v>1.9566791241904219E-10</v>
@@ -10155,12 +10152,12 @@
         <v>83</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D47" s="12">
         <v>1.2066187932507601E-7</v>
@@ -10178,12 +10175,12 @@
         <v>83</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D48" s="12">
         <v>2.5110715427110409E-7</v>
@@ -10201,12 +10198,12 @@
         <v>83</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D49" s="12">
         <v>3.3263545111237179E-7</v>
@@ -10224,12 +10221,12 @@
         <v>83</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D50" s="12">
         <v>1.6461867585001389E-4</v>
@@ -10247,7 +10244,7 @@
         <v>83</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -10256,7 +10253,7 @@
         <v>0</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -10272,7 +10269,7 @@
         <v>3</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -10296,7 +10293,7 @@
         <v>8</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -10350,13 +10347,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D60" s="12">
         <v>1</v>
@@ -10394,18 +10391,18 @@
         <v>26</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>129</v>
-      </c>
       <c r="C62" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D62" s="10">
         <v>9.8913792632769864E-5</v>
@@ -10420,18 +10417,18 @@
         <v>26</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B63" s="12" t="s">
-        <v>202</v>
-      </c>
       <c r="C63" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D63" s="10">
         <v>4.8958534751134958E-2</v>
@@ -10446,18 +10443,18 @@
         <v>26</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B64" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B64" s="12" t="s">
-        <v>204</v>
-      </c>
       <c r="C64" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D64" s="10">
         <v>2.1748021683655303E-3</v>
@@ -10472,18 +10469,18 @@
         <v>26</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D65" s="10">
         <v>2.9290775905960666</v>
@@ -10498,18 +10495,18 @@
         <v>26</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B66" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B66" s="12" t="s">
-        <v>160</v>
-      </c>
       <c r="C66" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D66" s="10">
         <v>12.094618558822805</v>
@@ -10524,7 +10521,7 @@
         <v>26</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -10550,18 +10547,18 @@
         <v>26</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B68" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="12" t="s">
-        <v>264</v>
-      </c>
       <c r="C68" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D68" s="10">
         <v>2.199915623999936E-2</v>
@@ -10576,7 +10573,7 @@
         <v>26</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -10602,18 +10599,18 @@
         <v>26</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>266</v>
-      </c>
       <c r="C70" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D70" s="10">
         <v>0.19432754583600303</v>
@@ -10628,15 +10625,15 @@
         <v>26</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B71" s="12" t="s">
         <v>267</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>268</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>24</v>
@@ -10654,15 +10651,15 @@
         <v>26</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>270</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>24</v>
@@ -10680,15 +10677,15 @@
         <v>26</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B73" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>24</v>
@@ -10706,18 +10703,18 @@
         <v>26</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B74" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="C74" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D74" s="10">
         <v>0.11891587183892328</v>
@@ -10732,18 +10729,18 @@
         <v>26</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B75" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="B75" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="C75" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D75" s="10">
         <v>2.1068396006041078E-4</v>
@@ -10758,15 +10755,15 @@
         <v>26</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B76" s="12" t="s">
         <v>267</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>268</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>24</v>
@@ -10784,18 +10781,18 @@
         <v>26</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B77" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="B77" s="12" t="s">
-        <v>276</v>
-      </c>
       <c r="C77" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D77" s="10">
         <v>7.3901853651316312E-3</v>
@@ -10810,18 +10807,18 @@
         <v>26</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B78" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="B78" s="12" t="s">
-        <v>276</v>
-      </c>
       <c r="C78" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D78" s="10">
         <v>3.5340535235939869E-5</v>
@@ -10836,7 +10833,7 @@
         <v>26</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -10862,7 +10859,7 @@
         <v>26</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -10888,7 +10885,7 @@
         <v>26</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -10914,15 +10911,15 @@
         <v>26</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B82" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>24</v>
@@ -10940,15 +10937,15 @@
         <v>26</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B83" s="12" t="s">
         <v>279</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>280</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>24</v>
@@ -10966,7 +10963,7 @@
         <v>26</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -10992,18 +10989,18 @@
         <v>26</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B85" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="B85" s="12" t="s">
-        <v>282</v>
-      </c>
       <c r="C85" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D85" s="10">
         <v>2.1680059115893879E-3</v>
@@ -11018,15 +11015,15 @@
         <v>26</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B86" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="B86" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>30</v>
@@ -11044,12 +11041,12 @@
         <v>26</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>58</v>
@@ -11070,15 +11067,15 @@
         <v>26</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B88" s="12" t="s">
         <v>286</v>
-      </c>
-      <c r="B88" s="12" t="s">
-        <v>287</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>24</v>
@@ -11096,15 +11093,15 @@
         <v>26</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B89" s="12" t="s">
         <v>286</v>
-      </c>
-      <c r="B89" s="12" t="s">
-        <v>287</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>24</v>
@@ -11122,15 +11119,15 @@
         <v>26</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="B90" s="12" t="s">
         <v>288</v>
-      </c>
-      <c r="B90" s="12" t="s">
-        <v>289</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>24</v>
@@ -11148,18 +11145,18 @@
         <v>26</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B91" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="B91" s="12" t="s">
-        <v>291</v>
-      </c>
       <c r="C91" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D91" s="10">
         <v>2.7185027104569126E-5</v>
@@ -11174,15 +11171,15 @@
         <v>26</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B92" s="12" t="s">
         <v>238</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>239</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>24</v>
@@ -11200,15 +11197,15 @@
         <v>26</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B93" s="12" t="s">
         <v>292</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>293</v>
       </c>
       <c r="C93" s="12" t="s">
         <v>30</v>
@@ -11226,7 +11223,7 @@
         <v>26</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -11237,7 +11234,7 @@
         <v>74</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D94" s="10">
         <v>1.9029518973198386E-4</v>
@@ -11252,7 +11249,7 @@
         <v>26</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -11278,15 +11275,15 @@
         <v>26</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B96" s="12" t="s">
         <v>294</v>
-      </c>
-      <c r="B96" s="12" t="s">
-        <v>295</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>24</v>
@@ -11304,18 +11301,18 @@
         <v>26</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B97" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="B97" s="12" t="s">
-        <v>297</v>
-      </c>
       <c r="C97" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D97" s="10">
         <v>5.2331177176295558E-5</v>
@@ -11330,15 +11327,15 @@
         <v>26</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B98" s="12" t="s">
         <v>298</v>
-      </c>
-      <c r="B98" s="12" t="s">
-        <v>299</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>24</v>
@@ -11356,18 +11353,18 @@
         <v>26</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B99" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B99" s="12" t="s">
-        <v>301</v>
-      </c>
       <c r="C99" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D99" s="10">
         <v>3.8173640122652792E-3</v>
@@ -11382,15 +11379,15 @@
         <v>26</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B100" s="12" t="s">
         <v>302</v>
-      </c>
-      <c r="B100" s="12" t="s">
-        <v>303</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>30</v>
@@ -11408,18 +11405,18 @@
         <v>26</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="B101" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B101" s="12" t="s">
-        <v>305</v>
-      </c>
       <c r="C101" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D101" s="36">
         <v>7.3127722911290904E-7</v>
@@ -11434,18 +11431,18 @@
         <v>26</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B102" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B102" s="12" t="s">
-        <v>307</v>
-      </c>
       <c r="C102" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D102" s="10">
         <v>1.0085645055795101E-5</v>
@@ -11460,15 +11457,15 @@
         <v>26</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="B103" s="12" t="s">
         <v>308</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>309</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>24</v>
@@ -11486,18 +11483,18 @@
         <v>26</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D104" s="10">
         <v>-1.413621409437595E-6</v>
@@ -11512,15 +11509,15 @@
         <v>26</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B105" s="12" t="s">
         <v>311</v>
-      </c>
-      <c r="B105" s="12" t="s">
-        <v>312</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>30</v>
@@ -11538,15 +11535,15 @@
         <v>26</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B106" s="12" t="s">
         <v>313</v>
-      </c>
-      <c r="B106" s="12" t="s">
-        <v>314</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>24</v>
@@ -11564,15 +11561,15 @@
         <v>26</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B107" s="12" t="s">
         <v>315</v>
-      </c>
-      <c r="B107" s="12" t="s">
-        <v>316</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>30</v>
@@ -11590,15 +11587,15 @@
         <v>26</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B108" s="12" t="s">
         <v>317</v>
-      </c>
-      <c r="B108" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>24</v>
@@ -11616,18 +11613,18 @@
         <v>26</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B109" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B109" s="12" t="s">
-        <v>190</v>
-      </c>
       <c r="C109" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D109" s="10">
         <v>-6.5719803025295877E-6</v>
@@ -11642,18 +11639,18 @@
         <v>26</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D110" s="10">
         <v>-1.453719324416834E-6</v>
@@ -11668,15 +11665,15 @@
         <v>26</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B111" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="B111" s="12" t="s">
-        <v>320</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>30</v>
@@ -11694,18 +11691,18 @@
         <v>26</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D112" s="10">
         <v>-5.4370054209138277E-9</v>
@@ -11720,7 +11717,7 @@
         <v>26</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -11731,7 +11728,7 @@
         <v>29</v>
       </c>
       <c r="C113" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D113" s="10">
         <v>-1.1813098880211155</v>
@@ -11748,13 +11745,13 @@
     </row>
     <row r="114" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D114" s="10">
         <v>-8.1455113913893665E-2</v>
@@ -11771,13 +11768,13 @@
     </row>
     <row r="115" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D115" s="10">
         <v>-0.11754425466185489</v>
@@ -11794,10 +11791,10 @@
     </row>
     <row r="116" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B116" s="17" t="s">
         <v>236</v>
-      </c>
-      <c r="B116" s="17" t="s">
-        <v>237</v>
       </c>
       <c r="C116" s="17" t="s">
         <v>30</v>
@@ -11815,12 +11812,12 @@
         <v>26</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D117" s="10">
         <v>0.49229365583664253</v>
@@ -11835,10 +11832,10 @@
         <v>45</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J117" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -11861,7 +11858,7 @@
         <v>83</v>
       </c>
       <c r="J118" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -11884,7 +11881,7 @@
         <v>83</v>
       </c>
       <c r="J119" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -11907,7 +11904,7 @@
         <v>83</v>
       </c>
       <c r="J120" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -11930,12 +11927,12 @@
         <v>83</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D122" s="10">
         <v>6.1166310985280523E-8</v>
@@ -11953,12 +11950,12 @@
         <v>83</v>
       </c>
       <c r="J122" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D123" s="10">
         <v>3.6624604119369031E-7</v>
@@ -11976,12 +11973,12 @@
         <v>83</v>
       </c>
       <c r="J123" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D124" s="10">
         <v>1.2783394395183524E-5</v>
@@ -11999,12 +11996,12 @@
         <v>83</v>
       </c>
       <c r="J124" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D125" s="10">
         <v>1.5971203423934363E-12</v>
@@ -12022,7 +12019,7 @@
         <v>86</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -12045,7 +12042,7 @@
         <v>86</v>
       </c>
       <c r="J126" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -12068,12 +12065,12 @@
         <v>86</v>
       </c>
       <c r="J127" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D128" s="10">
         <v>9.6539164721335606E-6</v>
@@ -12091,7 +12088,7 @@
         <v>86</v>
       </c>
       <c r="J128" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
@@ -12114,7 +12111,7 @@
         <v>86</v>
       </c>
       <c r="J129" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
@@ -12137,12 +12134,12 @@
         <v>86</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D131" s="10">
         <v>1.5631390585127251E-7</v>
@@ -12160,7 +12157,7 @@
         <v>86</v>
       </c>
       <c r="J131" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -12183,7 +12180,7 @@
         <v>86</v>
       </c>
       <c r="J132" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="133" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -12192,7 +12189,7 @@
         <v>0</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
@@ -12208,7 +12205,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
@@ -12232,7 +12229,7 @@
         <v>8</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
@@ -12286,13 +12283,13 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B142" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D142" s="12">
         <v>1</v>
@@ -12309,13 +12306,13 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B143" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D143" s="12">
         <v>1</v>
@@ -12332,13 +12329,13 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D144" s="10">
         <v>2.0840177703498237</v>
@@ -12387,7 +12384,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -12403,7 +12400,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -12427,7 +12424,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -12481,13 +12478,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -12510,7 +12507,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="10">
         <v>-1.0486557404129786</v>
@@ -12525,7 +12522,7 @@
         <v>26</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -12551,15 +12548,15 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>24</v>
@@ -12577,15 +12574,15 @@
         <v>26</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>30</v>
@@ -12603,15 +12600,15 @@
         <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>30</v>
@@ -12629,7 +12626,7 @@
         <v>26</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -12640,7 +12637,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D15" s="10">
         <v>0.10486557404129786</v>
@@ -12655,7 +12652,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -12666,7 +12663,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" s="10">
         <v>0.50335475539822994</v>
@@ -12681,18 +12678,18 @@
         <v>26</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B17" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>125</v>
       </c>
       <c r="D17" s="10">
         <v>1.3003331181120943</v>
@@ -12707,15 +12704,15 @@
         <v>26</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>30</v>
@@ -12733,15 +12730,15 @@
         <v>26</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>30</v>
@@ -12759,15 +12756,15 @@
         <v>26</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>30</v>
@@ -12785,15 +12782,15 @@
         <v>26</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>24</v>
@@ -12811,7 +12808,7 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -12820,7 +12817,7 @@
         <v>0</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -12836,7 +12833,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -12860,7 +12857,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -12914,13 +12911,13 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
@@ -12937,13 +12934,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
@@ -12960,10 +12957,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>30</v>
@@ -13015,7 +13012,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -13031,7 +13028,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -13055,7 +13052,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -13109,13 +13106,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -13138,7 +13135,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="10">
         <v>-1.1277867936282391</v>
@@ -13153,7 +13150,7 @@
         <v>26</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -13179,15 +13176,15 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>24</v>
@@ -13205,15 +13202,15 @@
         <v>26</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>24</v>
@@ -13231,15 +13228,15 @@
         <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>24</v>
@@ -13257,15 +13254,15 @@
         <v>26</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>30</v>
@@ -13283,15 +13280,15 @@
         <v>26</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>129</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>30</v>
@@ -13309,7 +13306,7 @@
         <v>26</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -13335,7 +13332,7 @@
         <v>26</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -13346,7 +13343,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D18" s="10">
         <v>1.0410339633491394</v>
@@ -13361,18 +13358,18 @@
         <v>26</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>125</v>
       </c>
       <c r="D19" s="10">
         <v>1.1277867936282351</v>
@@ -13387,15 +13384,15 @@
         <v>26</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>30</v>
@@ -13413,15 +13410,15 @@
         <v>26</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>30</v>
@@ -13439,15 +13436,15 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>30</v>
@@ -13465,7 +13462,7 @@
         <v>26</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -13474,7 +13471,7 @@
         <v>0</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -13490,7 +13487,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -13514,7 +13511,7 @@
         <v>8</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -13568,13 +13565,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
@@ -13591,13 +13588,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -13614,10 +13611,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>30</v>
@@ -13669,7 +13666,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -13677,7 +13674,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -13763,10 +13760,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>64</v>
@@ -13812,10 +13809,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
@@ -13838,10 +13835,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>30</v>
@@ -13890,10 +13887,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>24</v>
@@ -13916,10 +13913,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>30</v>
@@ -13942,10 +13939,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>30</v>
@@ -13968,10 +13965,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -14020,10 +14017,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>24</v>
@@ -14190,7 +14187,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D26" s="1">
         <v>6.6594639669227316E-5</v>
@@ -14213,7 +14210,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D27" s="1">
         <v>1.8406592952053521E-7</v>
@@ -14259,7 +14256,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D29" s="1">
         <v>5.0463018879787161E-7</v>
@@ -14328,7 +14325,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D32" s="1">
         <v>5.9149276227947258E-9</v>
@@ -14420,7 +14417,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D36" s="1">
         <v>6.2871957948587278E-5</v>
@@ -14447,7 +14444,7 @@
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -14541,7 +14538,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>2</v>
@@ -14590,10 +14587,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>30</v>
@@ -14616,10 +14613,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>30</v>
@@ -14642,10 +14639,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>30</v>
@@ -14668,10 +14665,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>30</v>
@@ -14720,10 +14717,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>30</v>
@@ -14746,10 +14743,10 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>30</v>
@@ -15043,7 +15040,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D66" s="1">
         <v>4.3882292204439848E-8</v>
@@ -15089,7 +15086,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D68" s="1">
         <v>2.9943211151264844E-6</v>
@@ -15116,7 +15113,7 @@
         <v>0</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -15210,7 +15207,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>2</v>
@@ -15233,7 +15230,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>2</v>
@@ -15256,10 +15253,10 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>64</v>
@@ -15311,7 +15308,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -15319,7 +15316,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -15327,7 +15324,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -15405,13 +15402,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -15449,7 +15446,7 @@
         <v>26</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -15472,7 +15469,7 @@
         <v>46</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -15495,12 +15492,12 @@
         <v>86</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" s="12">
         <v>1.4799999999999999E-4</v>
@@ -15518,7 +15515,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -15541,7 +15538,7 @@
         <v>46</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -15550,7 +15547,7 @@
         <v>0</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -15566,7 +15563,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -15590,7 +15587,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -15644,13 +15641,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D24" s="12">
         <v>1</v>
@@ -15673,7 +15670,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D25" s="10">
         <v>1.6909802294278311</v>
@@ -15688,15 +15685,15 @@
         <v>26</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>24</v>
@@ -15714,7 +15711,7 @@
         <v>26</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -15740,15 +15737,15 @@
         <v>26</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>30</v>
@@ -15766,15 +15763,15 @@
         <v>26</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>274</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>30</v>
@@ -15792,7 +15789,7 @@
         <v>26</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -15803,7 +15800,7 @@
         <v>38</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D30" s="22">
         <v>1.8</v>
@@ -15818,7 +15815,7 @@
         <v>26</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -15841,12 +15838,12 @@
         <v>46</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D32" s="10">
         <v>5.6574164890291897E-3</v>
@@ -15864,7 +15861,7 @@
         <v>86</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -15873,7 +15870,7 @@
         <v>0</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -15889,7 +15886,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -15913,7 +15910,7 @@
         <v>8</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -15967,13 +15964,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D42" s="12">
         <v>1</v>
@@ -15990,13 +15987,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D43" s="12">
         <v>1</v>
@@ -16013,13 +16010,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D44" s="10">
         <v>18.994348396149245</v>
@@ -16049,7 +16046,7 @@
   <cols>
     <col min="1" max="1" width="89.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
@@ -16076,8 +16073,8 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>363</v>
+      <c r="B3" s="2" t="s">
+        <v>361</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -16256,7 +16253,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -16348,13 +16345,13 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D15" s="1">
         <v>9.5907034946201408E-3</v>
@@ -16371,7 +16368,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>2</v>
@@ -16394,7 +16391,7 @@
     </row>
     <row r="17" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>2</v>
@@ -16417,7 +16414,7 @@
     </row>
     <row r="18" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>2</v>
@@ -16440,13 +16437,13 @@
     </row>
     <row r="19" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D19" s="1">
         <v>1.100027749289833E-3</v>
@@ -16463,13 +16460,13 @@
     </row>
     <row r="20" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D20" s="1">
         <v>6.0358175544023757E-2</v>
@@ -16486,13 +16483,13 @@
     </row>
     <row r="21" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D21" s="1">
         <v>0.10730342318937558</v>
@@ -16509,13 +16506,13 @@
     </row>
     <row r="22" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D22" s="1">
         <v>2.7647397631137553E-2</v>
@@ -16532,13 +16529,13 @@
     </row>
     <row r="23" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D23" s="1">
         <v>2.6799029941546548E-2</v>
@@ -16555,13 +16552,13 @@
     </row>
     <row r="24" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D24" s="1">
         <v>1.2222530547664812E-2</v>
@@ -16578,13 +16575,13 @@
     </row>
     <row r="25" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D25" s="1">
         <v>1.493864844714588E-2</v>
@@ -16601,13 +16598,13 @@
     </row>
     <row r="26" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D26" s="1">
         <v>1.493864844714588E-2</v>
@@ -16624,7 +16621,7 @@
     </row>
     <row r="27" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>2</v>
@@ -16647,13 +16644,13 @@
     </row>
     <row r="28" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D28" s="1">
         <v>6.8741255480693736E-2</v>
@@ -16703,7 +16700,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -16797,7 +16794,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>2</v>
@@ -17307,7 +17304,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>2</v>
@@ -17363,7 +17360,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -17457,7 +17454,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>2</v>
@@ -18019,7 +18016,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>2</v>
@@ -18977,7 +18974,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -18993,7 +18990,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -19071,13 +19068,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>95</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -19098,7 +19095,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -19106,7 +19103,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -19114,7 +19111,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -19138,7 +19135,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -19192,13 +19189,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="C19" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
@@ -19221,7 +19218,7 @@
         <v>38</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D20" s="10">
         <v>0.64556246497933512</v>
@@ -19236,12 +19233,12 @@
         <v>26</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" s="10">
         <v>9.781249469383868E-6</v>
@@ -19259,12 +19256,12 @@
         <v>86</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D22" s="10">
         <v>9.7812494693838658E-7</v>
@@ -19282,12 +19279,12 @@
         <v>86</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D23" s="10">
         <v>1.9562498938767732E-6</v>
@@ -19305,7 +19302,7 @@
         <v>86</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -19328,12 +19325,12 @@
         <v>86</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" s="10">
         <v>2.9343748408151604E-6</v>
@@ -19351,12 +19348,12 @@
         <v>86</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D26" s="10">
         <v>4.8906247346919329E-7</v>
@@ -19374,7 +19371,7 @@
         <v>86</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -19397,7 +19394,7 @@
         <v>86</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -19420,7 +19417,7 @@
         <v>86</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -19443,12 +19440,12 @@
         <v>86</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D30" s="10">
         <v>9.7812494693838665E-10</v>
@@ -19466,12 +19463,12 @@
         <v>86</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" s="10">
         <v>1.9562498938767732E-6</v>
@@ -19489,12 +19486,12 @@
         <v>86</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D32" s="10">
         <v>9.7812494693838682E-8</v>
@@ -19512,12 +19509,12 @@
         <v>86</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D33" s="10">
         <v>1.9562498938767737E-8</v>
@@ -19535,12 +19532,12 @@
         <v>86</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D34" s="10">
         <v>2.9343748408151604E-6</v>
@@ -19558,12 +19555,12 @@
         <v>86</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D35" s="10">
         <v>9.781249469383868E-6</v>
@@ -19581,7 +19578,7 @@
         <v>86</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -19590,7 +19587,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -19598,7 +19595,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -19606,7 +19603,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -19630,7 +19627,7 @@
         <v>8</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -19684,13 +19681,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>112</v>
-      </c>
       <c r="C45" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D45" s="12">
         <v>1</v>
@@ -19713,7 +19710,7 @@
         <v>38</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D46" s="10">
         <v>2.8162740366300702E-3</v>
@@ -19728,18 +19725,18 @@
         <v>26</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="C47" s="12" t="s">
         <v>115</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>116</v>
       </c>
       <c r="D47" s="10">
         <v>0.35203425457875875</v>
@@ -19754,7 +19751,7 @@
         <v>26</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -19777,7 +19774,7 @@
         <v>86</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -19800,12 +19797,12 @@
         <v>86</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D50" s="10">
         <v>2.112205527472553E-5</v>
@@ -19823,7 +19820,7 @@
         <v>86</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -19846,12 +19843,12 @@
         <v>86</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D52" s="10">
         <v>7.0406850915751763E-12</v>
@@ -19869,7 +19866,7 @@
         <v>86</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -19892,12 +19889,12 @@
         <v>86</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D54" s="10">
         <v>1.4081370183150353E-7</v>
@@ -19915,7 +19912,7 @@
         <v>86</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -19938,12 +19935,12 @@
         <v>86</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D56" s="10">
         <v>7.0406850915751763E-5</v>
@@ -19961,7 +19958,7 @@
         <v>86</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -19984,12 +19981,12 @@
         <v>86</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D58" s="10">
         <v>2.8162740366300702E-5</v>
@@ -20007,7 +20004,7 @@
         <v>86</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -20030,12 +20027,12 @@
         <v>86</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D60" s="10">
         <v>7.0406850915751765E-6</v>
@@ -20053,7 +20050,7 @@
         <v>86</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -20062,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -20070,7 +20067,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -20078,7 +20075,7 @@
         <v>3</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -20102,7 +20099,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -20156,13 +20153,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>122</v>
-      </c>
       <c r="C70" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D70" s="12">
         <v>1</v>
@@ -20185,7 +20182,7 @@
         <v>38</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D71" s="10">
         <v>4.5683571023683758</v>
@@ -20200,18 +20197,18 @@
         <v>26</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B72" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="C72" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>125</v>
       </c>
       <c r="D72" s="10">
         <v>5.8946543256366117E-4</v>
@@ -20226,7 +20223,7 @@
         <v>26</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
@@ -20237,7 +20234,7 @@
         <v>29</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D73" s="10">
         <v>0.58946543256366124</v>
@@ -20252,7 +20249,7 @@
         <v>26</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -20275,7 +20272,7 @@
         <v>86</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -20298,7 +20295,7 @@
         <v>86</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
@@ -20321,12 +20318,12 @@
         <v>86</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D77" s="10">
         <v>5.8946543256366118E-12</v>
@@ -20344,7 +20341,7 @@
         <v>86</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -20367,7 +20364,7 @@
         <v>86</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -20390,12 +20387,12 @@
         <v>86</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D80" s="10">
         <v>1.0315645069864072E-4</v>
@@ -20413,7 +20410,7 @@
         <v>86</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -20436,12 +20433,12 @@
         <v>86</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D82" s="10">
         <v>2.9473271628183065E-5</v>
@@ -20459,7 +20456,7 @@
         <v>86</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -20482,12 +20479,12 @@
         <v>86</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D84" s="10">
         <v>1.4736635814091532E-5</v>
@@ -20505,7 +20502,7 @@
         <v>86</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -20528,7 +20525,7 @@
         <v>83</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -20551,7 +20548,7 @@
         <v>83</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -20574,7 +20571,7 @@
         <v>83</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -20597,12 +20594,12 @@
         <v>83</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D89" s="10">
         <v>7.3683179070457636E-10</v>
@@ -20620,12 +20617,12 @@
         <v>83</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D90" s="10">
         <v>1.3262972232682381E-7</v>
@@ -20643,12 +20640,12 @@
         <v>83</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D91" s="10">
         <v>4.4209907442274596E-9</v>
@@ -20666,7 +20663,7 @@
         <v>83</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -20689,7 +20686,7 @@
         <v>86</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -20712,7 +20709,7 @@
         <v>86</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -20735,12 +20732,12 @@
         <v>86</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D95" s="10">
         <v>5.8946543256366125E-7</v>
@@ -20758,12 +20755,12 @@
         <v>86</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D96" s="10">
         <v>4.4209907442274598E-5</v>
@@ -20781,7 +20778,7 @@
         <v>86</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -20804,12 +20801,12 @@
         <v>86</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D98" s="10">
         <v>1.3262972232682375E-5</v>
@@ -20827,7 +20824,7 @@
         <v>86</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -20850,7 +20847,7 @@
         <v>83</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -20873,7 +20870,7 @@
         <v>83</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -20896,7 +20893,7 @@
         <v>83</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -20919,12 +20916,12 @@
         <v>83</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D103" s="10">
         <v>1.4736635814091531E-9</v>
@@ -20942,12 +20939,12 @@
         <v>83</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D104" s="10">
         <v>1.4736635814091528E-6</v>
@@ -20965,12 +20962,12 @@
         <v>83</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D105" s="10">
         <v>4.4209907442274597E-6</v>
@@ -20988,7 +20985,7 @@
         <v>83</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -20997,7 +20994,7 @@
         <v>0</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -21013,7 +21010,7 @@
         <v>3</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -21037,7 +21034,7 @@
         <v>8</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
@@ -21091,13 +21088,13 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B115" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D115" s="12">
         <v>1</v>
@@ -21114,13 +21111,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B116" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B116" s="12" t="s">
-        <v>122</v>
-      </c>
       <c r="C116" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D116" s="12">
         <v>1</v>
@@ -21137,13 +21134,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B117" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B117" s="12" t="s">
-        <v>112</v>
-      </c>
       <c r="C117" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D117" s="10">
         <v>0.43393674081112282</v>
@@ -21160,13 +21157,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B118" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B118" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="C118" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D118" s="10">
         <v>1.1617130401099041</v>
@@ -21183,13 +21180,13 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B119" s="12" t="s">
         <v>95</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D119" s="10">
         <v>9.7812494693838676</v>
@@ -21240,7 +21237,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -21248,7 +21245,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -21334,10 +21331,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>137</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>64</v>
@@ -21361,7 +21358,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -21401,7 +21398,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -21455,7 +21452,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>62</v>
@@ -21478,10 +21475,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>140</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>30</v>
@@ -21490,16 +21487,16 @@
         <v>5.5584817403615219</v>
       </c>
       <c r="E20" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -21525,15 +21522,15 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>144</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>145</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>30</v>
@@ -21551,15 +21548,15 @@
         <v>26</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>64</v>
@@ -21577,7 +21574,7 @@
         <v>26</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -21603,15 +21600,15 @@
         <v>26</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>144</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>145</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>30</v>
@@ -21629,15 +21626,15 @@
         <v>26</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>64</v>
@@ -21655,7 +21652,7 @@
         <v>26</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -21664,7 +21661,7 @@
         <v>0</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -21758,7 +21755,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>2</v>
@@ -21781,10 +21778,10 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>149</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>30</v>
@@ -21802,15 +21799,15 @@
         <v>26</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>30</v>
@@ -21828,7 +21825,7 @@
         <v>26</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -21854,15 +21851,15 @@
         <v>26</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>30</v>
@@ -21880,15 +21877,15 @@
         <v>26</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>129</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>30</v>
@@ -21906,15 +21903,15 @@
         <v>26</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>24</v>
@@ -21932,15 +21929,15 @@
         <v>26</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>30</v>
@@ -21958,15 +21955,15 @@
         <v>26</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>30</v>
@@ -21984,15 +21981,15 @@
         <v>26</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" s="12" t="s">
         <v>159</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>160</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>30</v>
@@ -22010,15 +22007,15 @@
         <v>26</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>64</v>
@@ -22036,12 +22033,12 @@
         <v>26</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D47" s="12">
         <v>3.260869565217391E-6</v>
@@ -22056,10 +22053,10 @@
         <v>45</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -22079,10 +22076,10 @@
         <v>45</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -22102,15 +22099,15 @@
         <v>45</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D50" s="12">
         <v>2.1739130434782609E-3</v>
@@ -22125,10 +22122,10 @@
         <v>45</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -22148,10 +22145,10 @@
         <v>45</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -22171,15 +22168,15 @@
         <v>45</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D53" s="12">
         <v>1.0869565217391299E-6</v>
@@ -22194,10 +22191,10 @@
         <v>45</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -22217,15 +22214,15 @@
         <v>45</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D55" s="12">
         <v>3.0652173913043478E-4</v>
@@ -22240,15 +22237,15 @@
         <v>45</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D56" s="12">
         <v>1.0217391304347831E-4</v>
@@ -22263,10 +22260,10 @@
         <v>45</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -22286,10 +22283,10 @@
         <v>45</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -22309,15 +22306,15 @@
         <v>45</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D59" s="12">
         <v>4.0760869565217389E-4</v>
@@ -22332,15 +22329,15 @@
         <v>45</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D60" s="12">
         <v>1.9130434782608691E-4</v>
@@ -22358,7 +22355,7 @@
         <v>86</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -22367,7 +22364,7 @@
         <v>0</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -22407,7 +22404,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -22461,7 +22458,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>2</v>
@@ -22484,7 +22481,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>2</v>
@@ -22507,7 +22504,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>62</v>
@@ -22530,10 +22527,10 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>137</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>64</v>
@@ -22586,7 +22583,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -22594,7 +22591,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -22680,10 +22677,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>166</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>64</v>
@@ -22707,7 +22704,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -22747,7 +22744,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -22801,7 +22798,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>62</v>
@@ -22824,10 +22821,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>140</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>30</v>
@@ -22836,24 +22833,24 @@
         <v>0.31560993702136675</v>
       </c>
       <c r="E20" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>64</v>
@@ -22871,7 +22868,7 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -22897,15 +22894,15 @@
         <v>26</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>30</v>
@@ -22923,15 +22920,15 @@
         <v>26</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>30</v>
@@ -22949,15 +22946,15 @@
         <v>26</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>64</v>
@@ -22975,7 +22972,7 @@
         <v>26</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -22984,7 +22981,7 @@
         <v>0</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -23078,7 +23075,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>2</v>
@@ -23101,10 +23098,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>149</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>30</v>
@@ -23122,15 +23119,15 @@
         <v>26</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>24</v>
@@ -23148,7 +23145,7 @@
         <v>26</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -23174,15 +23171,15 @@
         <v>26</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>30</v>
@@ -23200,15 +23197,15 @@
         <v>26</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>129</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>30</v>
@@ -23226,15 +23223,15 @@
         <v>26</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>24</v>
@@ -23252,15 +23249,15 @@
         <v>26</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>30</v>
@@ -23278,15 +23275,15 @@
         <v>26</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>30</v>
@@ -23304,15 +23301,15 @@
         <v>26</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" s="12" t="s">
         <v>159</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>160</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>30</v>
@@ -23330,15 +23327,15 @@
         <v>26</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>64</v>
@@ -23356,12 +23353,12 @@
         <v>26</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" s="12">
         <v>3.260869565217391E-6</v>
@@ -23376,10 +23373,10 @@
         <v>45</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -23399,10 +23396,10 @@
         <v>45</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -23422,15 +23419,15 @@
         <v>45</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D49" s="12">
         <v>2.1739130434782609E-3</v>
@@ -23445,10 +23442,10 @@
         <v>45</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -23468,10 +23465,10 @@
         <v>45</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -23491,15 +23488,15 @@
         <v>45</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D52" s="12">
         <v>1.0869565217391299E-6</v>
@@ -23514,10 +23511,10 @@
         <v>45</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -23537,15 +23534,15 @@
         <v>45</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D54" s="12">
         <v>3.0652173913043478E-4</v>
@@ -23560,15 +23557,15 @@
         <v>45</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D55" s="12">
         <v>1.0217391304347831E-4</v>
@@ -23583,10 +23580,10 @@
         <v>45</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -23606,10 +23603,10 @@
         <v>45</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -23629,15 +23626,15 @@
         <v>45</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D58" s="12">
         <v>4.0760869565217389E-4</v>
@@ -23652,15 +23649,15 @@
         <v>45</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D59" s="12">
         <v>1.9130434782608691E-4</v>
@@ -23678,7 +23675,7 @@
         <v>86</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -23687,7 +23684,7 @@
         <v>0</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -23727,7 +23724,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -23781,7 +23778,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>2</v>
@@ -23804,7 +23801,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>2</v>
@@ -23827,7 +23824,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>62</v>
@@ -23850,10 +23847,10 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>166</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>64</v>
@@ -23906,7 +23903,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -23914,7 +23911,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -24000,10 +23997,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>174</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>175</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>64</v>
@@ -24027,7 +24024,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -24067,7 +24064,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -24121,7 +24118,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>62</v>
@@ -24144,10 +24141,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>140</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>30</v>
@@ -24156,24 +24153,24 @@
         <v>1.8067674671839939</v>
       </c>
       <c r="E20" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>64</v>
@@ -24191,7 +24188,7 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -24217,15 +24214,15 @@
         <v>26</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>64</v>
@@ -24243,7 +24240,7 @@
         <v>26</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -24252,7 +24249,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -24346,7 +24343,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>2</v>
@@ -24369,10 +24366,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>149</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>30</v>
@@ -24390,15 +24387,15 @@
         <v>26</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>24</v>
@@ -24416,7 +24413,7 @@
         <v>26</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -24442,15 +24439,15 @@
         <v>26</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>30</v>
@@ -24468,15 +24465,15 @@
         <v>26</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>129</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>30</v>
@@ -24494,15 +24491,15 @@
         <v>26</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>24</v>
@@ -24520,15 +24517,15 @@
         <v>26</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>64</v>
@@ -24546,15 +24543,15 @@
         <v>26</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>30</v>
@@ -24572,15 +24569,15 @@
         <v>26</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>159</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>160</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>30</v>
@@ -24598,15 +24595,15 @@
         <v>26</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>64</v>
@@ -24624,12 +24621,12 @@
         <v>26</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D44" s="12">
         <v>3.260869565217391E-6</v>
@@ -24644,10 +24641,10 @@
         <v>45</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -24667,10 +24664,10 @@
         <v>45</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -24690,15 +24687,15 @@
         <v>45</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D47" s="12">
         <v>2.1739130434782609E-3</v>
@@ -24713,10 +24710,10 @@
         <v>45</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -24736,10 +24733,10 @@
         <v>45</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -24759,15 +24756,15 @@
         <v>45</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D50" s="12">
         <v>1.0869565217391299E-6</v>
@@ -24782,10 +24779,10 @@
         <v>45</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -24805,15 +24802,15 @@
         <v>45</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D52" s="12">
         <v>3.0652173913043478E-4</v>
@@ -24828,15 +24825,15 @@
         <v>45</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D53" s="12">
         <v>1.0217391304347831E-4</v>
@@ -24851,10 +24848,10 @@
         <v>45</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -24874,10 +24871,10 @@
         <v>45</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -24897,15 +24894,15 @@
         <v>45</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D56" s="12">
         <v>4.0760869565217389E-4</v>
@@ -24920,15 +24917,15 @@
         <v>45</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D57" s="12">
         <v>1.9130434782608691E-4</v>
@@ -24946,7 +24943,7 @@
         <v>86</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -24955,7 +24952,7 @@
         <v>0</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -24995,7 +24992,7 @@
         <v>8</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -25049,7 +25046,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>2</v>
@@ -25072,7 +25069,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>2</v>
@@ -25095,7 +25092,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>62</v>
@@ -25118,10 +25115,10 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>174</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>175</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>64</v>
@@ -25145,12 +25142,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25377,20 +25376,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AB9AAA4-2C14-419A-86E3-3A21FB19C946}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C275814-E995-49F2-A1D1-BF3CA46CD939}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
+    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25415,12 +25415,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C275814-E995-49F2-A1D1-BF3CA46CD939}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AB9AAA4-2C14-419A-86E3-3A21FB19C946}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
-    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>